--- a/DesignData/Config.xlsx
+++ b/DesignData/Config.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Progress" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lobby" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Interaction" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,4 +714,77 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>InteractionRange</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NPC를 조준해 상호작용할 수 있는 평면 거리(cm). 서버는 여기에 여유를 더해 판정한다. 0보다 크다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>